--- a/Data/Pun_ts_price.xlsx
+++ b/Data/Pun_ts_price.xlsx
@@ -67272,119 +67272,257 @@
       </c>
     </row>
     <row r="6086">
-      <c r="A6086" s="14"/>
-      <c r="B6086" s="11"/>
-      <c r="C6086" s="15"/>
+      <c r="A6086" s="12">
+        <v>46281.0</v>
+      </c>
+      <c r="B6086" s="2">
+        <v>2026.0</v>
+      </c>
+      <c r="C6086" s="13">
+        <v>227.736425</v>
+      </c>
     </row>
     <row r="6087">
-      <c r="A6087" s="14"/>
-      <c r="B6087" s="11"/>
-      <c r="C6087" s="15"/>
+      <c r="A6087" s="12">
+        <v>46282.0</v>
+      </c>
+      <c r="B6087" s="2">
+        <v>2026.0</v>
+      </c>
+      <c r="C6087" s="13">
+        <v>222.805008</v>
+      </c>
     </row>
     <row r="6088">
-      <c r="A6088" s="14"/>
-      <c r="B6088" s="11"/>
-      <c r="C6088" s="15"/>
+      <c r="A6088" s="12">
+        <v>46283.0</v>
+      </c>
+      <c r="B6088" s="2">
+        <v>2026.0</v>
+      </c>
+      <c r="C6088" s="13">
+        <v>220.825216</v>
+      </c>
     </row>
     <row r="6089">
-      <c r="A6089" s="14"/>
-      <c r="B6089" s="11"/>
-      <c r="C6089" s="15"/>
+      <c r="A6089" s="12">
+        <v>46284.0</v>
+      </c>
+      <c r="B6089" s="2">
+        <v>2026.0</v>
+      </c>
+      <c r="C6089" s="13">
+        <v>203.025973</v>
+      </c>
     </row>
     <row r="6090">
-      <c r="A6090" s="14"/>
-      <c r="B6090" s="11"/>
-      <c r="C6090" s="15"/>
+      <c r="A6090" s="12">
+        <v>46285.0</v>
+      </c>
+      <c r="B6090" s="2">
+        <v>2026.0</v>
+      </c>
+      <c r="C6090" s="13">
+        <v>186.817144</v>
+      </c>
     </row>
     <row r="6091">
-      <c r="A6091" s="14"/>
-      <c r="B6091" s="11"/>
-      <c r="C6091" s="15"/>
+      <c r="A6091" s="12">
+        <v>46286.0</v>
+      </c>
+      <c r="B6091" s="2">
+        <v>2026.0</v>
+      </c>
+      <c r="C6091" s="13">
+        <v>224.232069</v>
+      </c>
     </row>
     <row r="6092">
-      <c r="A6092" s="14"/>
-      <c r="B6092" s="11"/>
-      <c r="C6092" s="15"/>
+      <c r="A6092" s="12">
+        <v>46287.0</v>
+      </c>
+      <c r="B6092" s="2">
+        <v>2026.0</v>
+      </c>
+      <c r="C6092" s="13">
+        <v>215.249541</v>
+      </c>
     </row>
     <row r="6093">
-      <c r="A6093" s="14"/>
-      <c r="B6093" s="11"/>
-      <c r="C6093" s="15"/>
+      <c r="A6093" s="12">
+        <v>46288.0</v>
+      </c>
+      <c r="B6093" s="2">
+        <v>2026.0</v>
+      </c>
+      <c r="C6093" s="13">
+        <v>205.915295</v>
+      </c>
     </row>
     <row r="6094">
-      <c r="A6094" s="14"/>
-      <c r="B6094" s="11"/>
-      <c r="C6094" s="15"/>
+      <c r="A6094" s="12">
+        <v>46289.0</v>
+      </c>
+      <c r="B6094" s="2">
+        <v>2026.0</v>
+      </c>
+      <c r="C6094" s="13">
+        <v>209.302545</v>
+      </c>
     </row>
     <row r="6095">
-      <c r="A6095" s="14"/>
-      <c r="B6095" s="11"/>
-      <c r="C6095" s="15"/>
+      <c r="A6095" s="12">
+        <v>46290.0</v>
+      </c>
+      <c r="B6095" s="2">
+        <v>2026.0</v>
+      </c>
+      <c r="C6095" s="13">
+        <v>204.192696</v>
+      </c>
     </row>
     <row r="6096">
-      <c r="A6096" s="14"/>
-      <c r="B6096" s="11"/>
-      <c r="C6096" s="15"/>
+      <c r="A6096" s="12">
+        <v>46291.0</v>
+      </c>
+      <c r="B6096" s="2">
+        <v>2026.0</v>
+      </c>
+      <c r="C6096" s="13">
+        <v>178.598906</v>
+      </c>
     </row>
     <row r="6097">
-      <c r="A6097" s="14"/>
-      <c r="B6097" s="11"/>
-      <c r="C6097" s="15"/>
+      <c r="A6097" s="12">
+        <v>46292.0</v>
+      </c>
+      <c r="B6097" s="2">
+        <v>2026.0</v>
+      </c>
+      <c r="C6097" s="13">
+        <v>172.774581</v>
+      </c>
     </row>
     <row r="6098">
-      <c r="A6098" s="14"/>
-      <c r="B6098" s="11"/>
-      <c r="C6098" s="15"/>
+      <c r="A6098" s="12">
+        <v>46293.0</v>
+      </c>
+      <c r="B6098" s="2">
+        <v>2026.0</v>
+      </c>
+      <c r="C6098" s="13">
+        <v>203.552609</v>
+      </c>
     </row>
     <row r="6099">
-      <c r="A6099" s="14"/>
-      <c r="B6099" s="11"/>
-      <c r="C6099" s="15"/>
+      <c r="A6099" s="12">
+        <v>46294.0</v>
+      </c>
+      <c r="B6099" s="2">
+        <v>2026.0</v>
+      </c>
+      <c r="C6099" s="13">
+        <v>203.021543</v>
+      </c>
     </row>
     <row r="6100">
-      <c r="A6100" s="14"/>
-      <c r="B6100" s="11"/>
-      <c r="C6100" s="15"/>
+      <c r="A6100" s="12">
+        <v>46295.0</v>
+      </c>
+      <c r="B6100" s="2">
+        <v>2026.0</v>
+      </c>
+      <c r="C6100" s="13">
+        <v>201.961314</v>
+      </c>
     </row>
     <row r="6101">
-      <c r="A6101" s="14"/>
-      <c r="B6101" s="11"/>
-      <c r="C6101" s="15"/>
+      <c r="A6101" s="12">
+        <v>46296.0</v>
+      </c>
+      <c r="B6101" s="2">
+        <v>2026.0</v>
+      </c>
+      <c r="C6101" s="13">
+        <v>209.949464</v>
+      </c>
     </row>
     <row r="6102">
-      <c r="A6102" s="14"/>
-      <c r="B6102" s="11"/>
-      <c r="C6102" s="15"/>
+      <c r="A6102" s="12">
+        <v>46297.0</v>
+      </c>
+      <c r="B6102" s="2">
+        <v>2026.0</v>
+      </c>
+      <c r="C6102" s="13">
+        <v>216.173287</v>
+      </c>
     </row>
     <row r="6103">
-      <c r="A6103" s="14"/>
-      <c r="B6103" s="11"/>
-      <c r="C6103" s="15"/>
+      <c r="A6103" s="12">
+        <v>46298.0</v>
+      </c>
+      <c r="B6103" s="2">
+        <v>2026.0</v>
+      </c>
+      <c r="C6103" s="13">
+        <v>181.097191</v>
+      </c>
     </row>
     <row r="6104">
-      <c r="A6104" s="14"/>
-      <c r="B6104" s="11"/>
-      <c r="C6104" s="15"/>
+      <c r="A6104" s="12">
+        <v>46299.0</v>
+      </c>
+      <c r="B6104" s="2">
+        <v>2026.0</v>
+      </c>
+      <c r="C6104" s="13">
+        <v>191.942749</v>
+      </c>
     </row>
     <row r="6105">
-      <c r="A6105" s="14"/>
-      <c r="B6105" s="11"/>
-      <c r="C6105" s="15"/>
+      <c r="A6105" s="12">
+        <v>46300.0</v>
+      </c>
+      <c r="B6105" s="2">
+        <v>2026.0</v>
+      </c>
+      <c r="C6105" s="13">
+        <v>210.091367</v>
+      </c>
     </row>
     <row r="6106">
-      <c r="A6106" s="14"/>
-      <c r="B6106" s="11"/>
-      <c r="C6106" s="15"/>
+      <c r="A6106" s="12">
+        <v>46301.0</v>
+      </c>
+      <c r="B6106" s="2">
+        <v>2026.0</v>
+      </c>
+      <c r="C6106" s="13">
+        <v>233.266634</v>
+      </c>
     </row>
     <row r="6107">
-      <c r="A6107" s="14"/>
-      <c r="B6107" s="11"/>
-      <c r="C6107" s="15"/>
+      <c r="A6107" s="12">
+        <v>46302.0</v>
+      </c>
+      <c r="B6107" s="2">
+        <v>2026.0</v>
+      </c>
+      <c r="C6107" s="13">
+        <v>220.273117</v>
+      </c>
     </row>
     <row r="6108">
-      <c r="A6108" s="14"/>
-      <c r="B6108" s="11"/>
-      <c r="C6108" s="15"/>
+      <c r="A6108" s="12">
+        <v>46303.0</v>
+      </c>
+      <c r="B6108" s="2">
+        <v>2026.0</v>
+      </c>
+      <c r="C6108" s="13">
+        <v>218.835259</v>
+      </c>
     </row>
     <row r="6109">
       <c r="A6109" s="14"/>
